--- a/data/Diessenhofen/investment_decision/Diessenhofen_SFH_until_2004_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Diessenhofen_SFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>226.2122281393881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>291659.3969201751</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>226.3750672528683</v>
       </c>
       <c r="G2" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>204.6416768207457</v>
       </c>
       <c r="I2" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>205.4570524259056</v>
       </c>
       <c r="K2" t="n">
         <v>291659.3969201751</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>377.5900355588477</v>
+        <v>411.8201282018625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>291659.3969201751</v>
       </c>
       <c r="F3" t="n">
-        <v>492.4847335235025</v>
+        <v>477.0504154632538</v>
       </c>
       <c r="G3" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="H3" t="n">
-        <v>470.2661841648</v>
+        <v>380.1524034030881</v>
       </c>
       <c r="I3" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="J3" t="n">
-        <v>328.6585585485513</v>
+        <v>467.1132187307788</v>
       </c>
       <c r="K3" t="n">
         <v>291659.3969201751</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>1171.109563186159</v>
+        <v>1167.177719448885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>291659.3969201751</v>
       </c>
       <c r="F4" t="n">
-        <v>1217.433587470541</v>
+        <v>1160.979619603589</v>
       </c>
       <c r="G4" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="H4" t="n">
-        <v>1089.228462678062</v>
+        <v>1159.30549704013</v>
       </c>
       <c r="I4" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="J4" t="n">
-        <v>955.1260870651414</v>
+        <v>1160.909953677331</v>
       </c>
       <c r="K4" t="n">
         <v>291659.3969201751</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>1499.684680546371</v>
+        <v>1600.714135280037</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>291659.3969201751</v>
       </c>
       <c r="F5" t="n">
-        <v>1385.441908599423</v>
+        <v>1540.952556990838</v>
       </c>
       <c r="G5" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="H5" t="n">
-        <v>1282.736644137101</v>
+        <v>1573.437332935492</v>
       </c>
       <c r="I5" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="J5" t="n">
-        <v>1242.951981156784</v>
+        <v>1538.416243347022</v>
       </c>
       <c r="K5" t="n">
         <v>291659.3969201751</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>1499.684680546371</v>
+        <v>1600.714135280037</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>291659.3969201751</v>
       </c>
       <c r="F6" t="n">
-        <v>1385.441908599423</v>
+        <v>1540.952556990838</v>
       </c>
       <c r="G6" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="H6" t="n">
-        <v>1282.736644137101</v>
+        <v>1573.437332935492</v>
       </c>
       <c r="I6" t="n">
         <v>291659.3969201751</v>
       </c>
       <c r="J6" t="n">
-        <v>1242.951981156784</v>
+        <v>1538.416243347022</v>
       </c>
       <c r="K6" t="n">
         <v>291659.3969201751</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>255.4508862267819</v>
+        <v>217.5934009362292</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>255.4508862267819</v>
+        <v>217.5934009362292</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>339.0511693620709</v>
+        <v>288.8042320878968</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>339.0511693620709</v>
+        <v>288.8042320878968</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>375.5582836221167</v>
+        <v>319.9010400400865</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>375.5582836221167</v>
+        <v>319.9010400400865</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>394.5333511386143</v>
+        <v>336.0640275125347</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>394.5333511386143</v>
+        <v>336.0640275125347</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Diessenhofen_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Diessenhofen_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>437.4890953802625</v>
+        <v>372.653786966292</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>405.5978876790064</v>
+        <v>345.4888142931518</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>405.5978876790064</v>
+        <v>345.4888142931518</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.048630087148339</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.04851514189176474</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.05016734174117648</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.05016734174117647</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.0501673417411765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.05261107838214362</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.05016734174117647</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05769244300235295</v>
+        <v>0.0526757088282353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.05957048544</v>
+        <v>0.05706211835294119</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05957048544</v>
+        <v>0.05706211835294119</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06020081008941177</v>
+        <v>0.05706211835294119</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06020081008941177</v>
+        <v>0.05706211835294119</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06375892064209095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06542039853462607</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06270917717647059</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06270917717647059</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06375892064209095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06542039853462607</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06270917717647059</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06772591135058822</v>
+        <v>0.06270917717647059</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2.107463813889184</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>44.774352504</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.224803683479901</v>
       </c>
       <c r="G20" t="n">
         <v>44.774352504</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.665140029999992</v>
       </c>
       <c r="I20" t="n">
         <v>44.774352504</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.665140029999999</v>
       </c>
       <c r="K20" t="n">
         <v>44.774352504</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>2.107463813889184</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>44.774352504</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.224803683479901</v>
       </c>
       <c r="G21" t="n">
         <v>44.774352504</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.665140029999992</v>
       </c>
       <c r="I21" t="n">
         <v>44.774352504</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.665140029999999</v>
       </c>
       <c r="K21" t="n">
         <v>44.774352504</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>31.86204577347432</v>
+        <v>38.60583561386292</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2364,13 +2364,13 @@
         <v>433.0611407440217</v>
       </c>
       <c r="H52" t="n">
-        <v>35.63205391427768</v>
+        <v>20.56478383183519</v>
       </c>
       <c r="I52" t="n">
         <v>145.3132484005243</v>
       </c>
       <c r="J52" t="n">
-        <v>21.01577937486893</v>
+        <v>36.96837571166426</v>
       </c>
       <c r="K52" t="n">
         <v>145.3132484005243</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>48.69979930102316</v>
+        <v>53.25761990846519</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F53" t="n">
-        <v>58.30862118680783</v>
+        <v>56.33648263698221</v>
       </c>
       <c r="G53" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H53" t="n">
-        <v>50.42548063434231</v>
+        <v>36.57042689482321</v>
       </c>
       <c r="I53" t="n">
         <v>219.4318499679698</v>
       </c>
       <c r="J53" t="n">
-        <v>38.9329037188214</v>
+        <v>49.25626945462771</v>
       </c>
       <c r="K53" t="n">
         <v>219.4318499679698</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>98.96217704826014</v>
+        <v>109.63378233831</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F54" t="n">
-        <v>107.7629749317592</v>
+        <v>109.0164638271161</v>
       </c>
       <c r="G54" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H54" t="n">
-        <v>99.85980556940869</v>
+        <v>91.7047983657632</v>
       </c>
       <c r="I54" t="n">
         <v>262.5025183508585</v>
       </c>
       <c r="J54" t="n">
-        <v>89.61872282181311</v>
+        <v>101.955953476721</v>
       </c>
       <c r="K54" t="n">
         <v>262.5025183508585</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>109.9995905659995</v>
+        <v>111.6791386653601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F55" t="n">
-        <v>106.2406722800797</v>
+        <v>109.4054312391735</v>
       </c>
       <c r="G55" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H55" t="n">
-        <v>104.143308650081</v>
+        <v>111.5780540449068</v>
       </c>
       <c r="I55" t="n">
         <v>289.9827045170326</v>
       </c>
       <c r="J55" t="n">
-        <v>108.6917021016215</v>
+        <v>109.0778980039342</v>
       </c>
       <c r="K55" t="n">
         <v>289.9827045170326</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>109.9995905659995</v>
+        <v>111.6791386653601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F56" t="n">
-        <v>106.2406722800797</v>
+        <v>109.4054312391735</v>
       </c>
       <c r="G56" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H56" t="n">
-        <v>104.143308650081</v>
+        <v>111.5780540449068</v>
       </c>
       <c r="I56" t="n">
         <v>308.7236463498119</v>
       </c>
       <c r="J56" t="n">
-        <v>108.6917021016215</v>
+        <v>109.0778980039341</v>
       </c>
       <c r="K56" t="n">
         <v>308.7236463498119</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>47.23351502568998</v>
+        <v>0.6069936495064455</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F64" t="n">
-        <v>49.55412741798165</v>
+        <v>6.833545676049947</v>
       </c>
       <c r="G64" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H64" t="n">
-        <v>51.91209539184695</v>
+        <v>0.7613420464566967</v>
       </c>
       <c r="I64" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="J64" t="n">
-        <v>50.49504423855409</v>
+        <v>6.859479885690096</v>
       </c>
       <c r="K64" t="n">
         <v>433.0611407440217</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>61.09138473059804</v>
+        <v>11.58848015043835</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F65" t="n">
-        <v>67.37036416240633</v>
+        <v>15.52983897403994</v>
       </c>
       <c r="G65" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H65" t="n">
-        <v>71.73328509672099</v>
+        <v>12.45072601945784</v>
       </c>
       <c r="I65" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="J65" t="n">
-        <v>68.06249450504045</v>
+        <v>15.92814823483743</v>
       </c>
       <c r="K65" t="n">
         <v>433.0611407440217</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>61.09138473059804</v>
+        <v>11.58848015043835</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>433.0611407440217</v>
       </c>
       <c r="F66" t="n">
-        <v>67.37036416240635</v>
+        <v>15.52983897403994</v>
       </c>
       <c r="G66" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="H66" t="n">
-        <v>71.73328509672099</v>
+        <v>12.45072601945784</v>
       </c>
       <c r="I66" t="n">
         <v>433.0611407440217</v>
       </c>
       <c r="J66" t="n">
-        <v>68.06249450504045</v>
+        <v>15.92814823483743</v>
       </c>
       <c r="K66" t="n">
         <v>433.0611407440217</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>17.25215070224734</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>17.25215070224734</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>29.55155757388174</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>29.55155757388174</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>39.25575667950213</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>39.25575667950213</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>47.32226355746911</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47.32226355746911</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>54.23995917392102</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>54.23995917392102</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="77">
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>12.14326375265206</v>
+        <v>5.399473912263458</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3289,16 +3289,16 @@
         <v>433.0611407440217</v>
       </c>
       <c r="H77" t="n">
-        <v>8.373255611848684</v>
+        <v>23.44052569429119</v>
       </c>
       <c r="I77" t="n">
-        <v>17.25215070224734</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J77" t="n">
-        <v>22.98953015125743</v>
+        <v>7.036933814462122</v>
       </c>
       <c r="K77" t="n">
-        <v>17.25215070224734</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>12.14326375265206</v>
+        <v>5.399473912263458</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3326,16 +3326,16 @@
         <v>433.0611407440217</v>
       </c>
       <c r="H78" t="n">
-        <v>8.373255611848684</v>
+        <v>23.44052569429119</v>
       </c>
       <c r="I78" t="n">
-        <v>29.55155757388174</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J78" t="n">
-        <v>22.98953015125743</v>
+        <v>7.036933814462122</v>
       </c>
       <c r="K78" t="n">
-        <v>29.55155757388174</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>12.14326375265206</v>
+        <v>5.399473912263458</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3363,16 +3363,16 @@
         <v>433.0611407440217</v>
       </c>
       <c r="H79" t="n">
-        <v>8.373255611848684</v>
+        <v>23.44052569429119</v>
       </c>
       <c r="I79" t="n">
-        <v>39.25575667950213</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J79" t="n">
-        <v>22.98953015125743</v>
+        <v>7.036933814462122</v>
       </c>
       <c r="K79" t="n">
-        <v>39.25575667950213</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>47.32226355746911</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>47.32226355746911</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>54.23995917392102</v>
+        <v>433.0611407440217</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>54.23995917392102</v>
+        <v>433.0611407440217</v>
       </c>
     </row>
     <row r="82">
